--- a/results/Int Task Remove ACC 0.5/Rando_7_permute.xlsx
+++ b/results/Int Task Remove ACC 0.5/Rando_7_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8169729061821529</v>
+        <v>0.776113317792074</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8169729061821529</v>
+        <v>0.776113317792074</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8234249467228286</v>
+        <v>0.7659218701537784</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8100618815595955</v>
+        <v>0.7659218701537784</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8126969754574833</v>
+        <v>0.7646199561776506</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8117127234889794</v>
+        <v>0.7669373880679147</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8154258671922681</v>
+        <v>0.7662707981070347</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8157122632542597</v>
+        <v>0.7750715364836066</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8139000890454131</v>
+        <v>0.7725615063682478</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.808916297311629</v>
+        <v>0.7514807551851445</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8168578475022261</v>
+        <v>0.723572772113778</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8168578475022261</v>
+        <v>0.6626779657625389</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8232060851034028</v>
+        <v>0.6626779657625389</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8173005732923792</v>
+        <v>0.6567724539515153</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8244454671882659</v>
+        <v>0.6488984382034838</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8185086894316101</v>
+        <v>0.6321661547389168</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8251745890404106</v>
+        <v>0.6400401704869483</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8241903370719067</v>
+        <v>0.663344555723419</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8264765030165384</v>
+        <v>0.6206727931244935</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8254609851024022</v>
+        <v>0.6170534472581016</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8029482536093407</v>
+        <v>0.6130539074928214</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8358450309657925</v>
+        <v>0.604862229737166</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8275595553732404</v>
+        <v>0.6160066633983332</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8219717055698406</v>
+        <v>0.6210217210777497</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7826016268296832</v>
+        <v>0.6199749372179811</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7826016268296832</v>
+        <v>0.6757283714694494</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7817737045893406</v>
+        <v>0.693856366747041</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7951105063582427</v>
+        <v>0.693856366747041</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7729304445267087</v>
+        <v>0.6820453431249938</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7637857807481816</v>
+        <v>0.6171159791493662</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7463556413771023</v>
+        <v>0.6387382565108205</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7463556413771023</v>
+        <v>0.5759699946972956</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7212178210887552</v>
+        <v>0.5736838287526639</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7619836116419374</v>
+        <v>0.5736838287526639</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7524637565158231</v>
+        <v>0.5789540165484397</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7534842769812604</v>
+        <v>0.5595866391859848</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8030145374140811</v>
+        <v>0.5573004732413531</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8153983531601117</v>
+        <v>0.5586336531631132</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8190176990265035</v>
+        <v>0.5619040710762488</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8373695584748222</v>
+        <v>0.6207665909613903</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8388640706760448</v>
+        <v>0.6457843500185094</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7830793704789443</v>
+        <v>0.676358692933396</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7820951185104403</v>
+        <v>0.6720414911604918</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7386317021681057</v>
+        <v>0.6697240592702278</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7129473531501065</v>
+        <v>0.7461105163633452</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6421750092547199</v>
+        <v>0.7550938478624099</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6424926712623438</v>
+        <v>0.7543647260102653</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6802744399643819</v>
+        <v>0.7463656464797046</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7067191767801579</v>
+        <v>0.7473498984482085</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7086876807171658</v>
+        <v>0.7632855256180653</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7482453551311168</v>
+        <v>0.6568349858427798</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6833159911554894</v>
+        <v>0.6062266756045583</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6594075478494031</v>
+        <v>0.5397815385846781</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6476903220642528</v>
+        <v>0.5309232708681427</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6312181712673464</v>
+        <v>0.5279705149626309</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6323274870183794</v>
+        <v>0.5266686009865031</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6907422785620667</v>
+        <v>0.5266686009865031</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6939188986383056</v>
+        <v>0.5158418293329599</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6938876326926733</v>
+        <v>0.5135243974426957</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6672190317061701</v>
+        <v>0.5019997698826402</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6479454521806122</v>
+        <v>0.5040620716565448</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6490235019860129</v>
+        <v>0.503426747641297</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6457843500185094</v>
+        <v>0.5073324895696806</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6586421575003252</v>
+        <v>0.5073324895696806</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5958788982381015</v>
+        <v>0.5066658996088005</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5846719326856697</v>
+        <v>0.5073637555153128</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5517176259892544</v>
+        <v>0.5073950214609451</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5076501515773044</v>
+        <v>0.5312671962700978</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5281268446907923</v>
+        <v>0.5309495342624738</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5133630651632333</v>
+        <v>0.550567039189987</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.530855736425577</v>
+        <v>0.550567039189987</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5298714844570731</v>
+        <v>0.6393910894556224</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5155554332709682</v>
+        <v>0.6147822889673733</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5168886131927283</v>
+        <v>0.582592121982211</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5029840218511441</v>
+        <v>0.5632197420684549</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.501650841929384</v>
+        <v>0.5144336111416823</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.501650841929384</v>
+        <v>0.518026693613743</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.502317431890264</v>
+        <v>0.5184068875126314</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5019997698826402</v>
+        <v>0.5096624278381975</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5003489279532561</v>
+        <v>0.5096624278381975</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5010155179141362</v>
+        <v>0.5077039290037919</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5009842519685039</v>
+        <v>0.5047149046013467</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5006665899608801</v>
+        <v>0.5093535202953506</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5009842519685039</v>
+        <v>0.4993184023852165</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5</v>
+        <v>0.4980327467008174</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5</v>
+        <v>0.4983504087084413</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5</v>
+        <v>0.4983504087084413</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5</v>
+        <v>0.4983504087084413</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5</v>
+        <v>0.4869921159791494</v>
       </c>
     </row>
   </sheetData>
